--- a/tame_output/ON/bt/strategyON_20231220.xlsx
+++ b/tame_output/ON/bt/strategyON_20231220.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373821</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502549</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728032</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702056</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823382</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714844</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083877</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666734</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097099</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762259</v>
+        <v>3.169279212762258</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.185514355963478</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583693</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742723</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589523</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872956</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.312164595946328</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336486</v>
+        <v>3.300520058336485</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43048,7 +43048,7 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.318449829143339</v>
+        <v>3.318449829143338</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308503</v>
+        <v>3.311781349308502</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257516</v>
+        <v>3.271427670257515</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.25296238744154</v>
+        <v>3.252962387441539</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662168</v>
+        <v>3.241257540662167</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543324</v>
+        <v>3.285495323543323</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978608</v>
+        <v>3.287726162978607</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,7 +43209,7 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621267</v>
+        <v>3.275586179621266</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
@@ -43232,7 +43232,7 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.268822948291748</v>
+        <v>3.268822948291747</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
@@ -43278,7 +43278,7 @@
         <v>45278</v>
       </c>
       <c r="B1816" t="n">
-        <v>3.291576855321623</v>
+        <v>3.291576855321622</v>
       </c>
       <c r="C1816" t="n">
         <v>3.127125924287274</v>
@@ -43301,22 +43301,22 @@
         <v>45279</v>
       </c>
       <c r="B1817" t="n">
-        <v>3.11631864538613</v>
+        <v>3.116318645386129</v>
       </c>
       <c r="C1817" t="n">
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>0.2949709124476316</v>
+        <v>0.2949199898034128</v>
       </c>
       <c r="E1817" t="n">
-        <v>3.243785915336657</v>
+        <v>3.243765546278969</v>
       </c>
       <c r="F1817" t="n">
-        <v>1.794754178127042</v>
+        <v>1.794574819729893</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.203006481547577</v>
+        <v>4.202898866509288</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231220.xlsx
+++ b/tame_output/ON/bt/strategyON_20231220.xlsx
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.128298755003009</v>
+        <v>3.12829875500301</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167863</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216944</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.13201899645404</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780869</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.095206606537932</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844645</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.12341686637382</v>
+        <v>3.123416866373821</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502549</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.146730118728032</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702056</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487811</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -43307,16 +43307,16 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>0.2949199898034128</v>
+        <v>0.2952118539543306</v>
       </c>
       <c r="E1817" t="n">
-        <v>3.243765546278969</v>
+        <v>3.243882291939336</v>
       </c>
       <c r="F1817" t="n">
-        <v>1.794574819729893</v>
+        <v>1.794561746776049</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.202898866509288</v>
+        <v>4.202891022736982</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231220.xlsx
+++ b/tame_output/ON/bt/strategyON_20231220.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>474.9%</t>
+          <t>475.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-112.9%</t>
+          <t>-114.8%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.8%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-38.1%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.5%</t>
+          <t>112.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -43307,16 +43307,16 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>0.2952118539543306</v>
+        <v>0.2763455303490789</v>
       </c>
       <c r="E1817" t="n">
-        <v>3.243882291939336</v>
+        <v>3.236335762497236</v>
       </c>
       <c r="F1817" t="n">
-        <v>1.794561746776049</v>
+        <v>1.711877279829487</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.202891022736982</v>
+        <v>4.153280342569045</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231220.xlsx
+++ b/tame_output/ON/bt/strategyON_20231220.xlsx
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.12829875500301</v>
+        <v>3.128298755003009</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167863</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216944</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.13201899645404</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780869</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537932</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373821</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502549</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728032</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702056</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
